--- a/data/trans_camb/IP19C02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,74; -1,36</t>
+          <t>-18,78; -0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 29,74</t>
+          <t>-4,13; 31,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 47,96</t>
+          <t>7,27; 47,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 8,11</t>
+          <t>-5,79; 6,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,29; 51,6</t>
+          <t>19,36; 49,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 60,72</t>
+          <t>22,87; 61,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 0,79</t>
+          <t>-10,97; 0,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,68; 36,25</t>
+          <t>12,13; 35,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,94; 49,04</t>
+          <t>19,19; 48,2</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-93,74; 8,76</t>
+          <t>-92,96; 44,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,25; 331,08</t>
+          <t>-25,19; 361,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,3; 578,66</t>
+          <t>25,77; 484,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>183,34; —</t>
+          <t>167,78; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>271,38; —</t>
+          <t>189,22; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,84; 54,94</t>
+          <t>-87,23; 29,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>93,04; 596,06</t>
+          <t>94,43; 621,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>159,47; 876,8</t>
+          <t>151,53; 856,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 3,25</t>
+          <t>-4,41; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 16,76</t>
+          <t>7,59; 17,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,11; 28,85</t>
+          <t>18,65; 29,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,33</t>
+          <t>-4,1; 3,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 18,82</t>
+          <t>8,43; 18,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,35; 32,55</t>
+          <t>20,73; 32,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,08</t>
+          <t>-2,85; 2,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,63; 16,22</t>
+          <t>9,76; 16,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,38; 29,55</t>
+          <t>21,25; 29,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,06; 72,34</t>
+          <t>-51,64; 73,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,45; 365,45</t>
+          <t>83,15; 361,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>203,73; 615,43</t>
+          <t>219,67; 646,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,98; 67,05</t>
+          <t>-48,34; 73,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>102,06; 391,38</t>
+          <t>95,31; 406,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>244,44; 712,33</t>
+          <t>233,79; 683,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 39,14</t>
+          <t>-38,05; 44,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>113,73; 307,58</t>
+          <t>126,84; 319,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>269,01; 575,0</t>
+          <t>274,74; 592,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 5,84</t>
+          <t>-6,29; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 20,27</t>
+          <t>3,3; 19,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,96; 27,64</t>
+          <t>11,56; 27,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 7,52</t>
+          <t>-7,96; 7,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 10,76</t>
+          <t>-5,65; 11,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,55; 23,54</t>
+          <t>6,06; 23,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 4,54</t>
+          <t>-4,73; 5,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 12,81</t>
+          <t>1,36; 12,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 23,7</t>
+          <t>11,16; 22,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,52; 235,92</t>
+          <t>-72,57; 234,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,18; 774,36</t>
+          <t>8,7; 615,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80,97; 1193,76</t>
+          <t>95,47; 973,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 149,01</t>
+          <t>-61,21; 160,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,0; 193,06</t>
+          <t>-46,05; 223,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,35; 424,49</t>
+          <t>33,84; 426,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 91,36</t>
+          <t>-50,61; 113,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 250,52</t>
+          <t>12,68; 259,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109,08; 518,71</t>
+          <t>104,93; 462,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,55</t>
+          <t>-4,69; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,62</t>
+          <t>7,84; 15,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,88</t>
+          <t>17,83; 27,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,72</t>
+          <t>-3,35; 2,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,86; 16,75</t>
+          <t>8,77; 17,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,39; 29,93</t>
+          <t>20,17; 30,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,21</t>
+          <t>-3,19; 1,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 14,93</t>
+          <t>9,57; 15,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,09</t>
+          <t>20,2; 27,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 28,52</t>
+          <t>-50,66; 29,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,22; 271,1</t>
+          <t>85,75; 277,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195,61; 482,5</t>
+          <t>195,16; 490,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 51,73</t>
+          <t>-40,42; 52,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>109,15; 321,82</t>
+          <t>105,21; 330,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>238,63; 593,22</t>
+          <t>233,43; 562,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 20,54</t>
+          <t>-40,26; 18,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>112,14; 258,28</t>
+          <t>118,61; 253,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>250,88; 465,36</t>
+          <t>242,06; 445,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -0,92</t>
+          <t>-20,34; -1,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 31,05</t>
+          <t>-2,98; 31,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 47,82</t>
+          <t>5,59; 47,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 6,74</t>
+          <t>-5,94; 7,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,36; 49,94</t>
+          <t>19,72; 51,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,87; 61,59</t>
+          <t>26,25; 62,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 0,6</t>
+          <t>-11,2; 0,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 35,83</t>
+          <t>12,11; 35,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,19; 48,2</t>
+          <t>19,09; 48,93</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,96; 44,41</t>
+          <t>-100,0; -3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 361,17</t>
+          <t>-22,65; 353,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,77; 484,34</t>
+          <t>26,1; 520,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>167,78; —</t>
+          <t>213,62; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>189,22; —</t>
+          <t>283,3; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,23; 29,7</t>
+          <t>-86,59; 49,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,43; 621,06</t>
+          <t>94,69; 670,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>151,53; 856,25</t>
+          <t>147,85; 875,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 3,45</t>
+          <t>-4,11; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,26</t>
+          <t>7,47; 17,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,65; 29,41</t>
+          <t>17,64; 28,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,21</t>
+          <t>-4,35; 3,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 18,7</t>
+          <t>8,86; 19,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,73; 32,86</t>
+          <t>20,46; 32,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,33</t>
+          <t>-2,97; 2,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 16,54</t>
+          <t>9,56; 16,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,25; 29,43</t>
+          <t>21,16; 29,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 73,73</t>
+          <t>-48,83; 68,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,15; 361,22</t>
+          <t>83,47; 351,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>219,67; 646,77</t>
+          <t>192,45; 631,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,34; 73,77</t>
+          <t>-52,41; 64,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,31; 406,4</t>
+          <t>101,6; 407,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>233,79; 683,95</t>
+          <t>229,59; 688,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,05; 44,34</t>
+          <t>-40,59; 37,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>126,84; 319,48</t>
+          <t>120,41; 306,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>274,74; 592,77</t>
+          <t>264,7; 540,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 6,06</t>
+          <t>-5,66; 6,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 19,39</t>
+          <t>3,25; 20,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 27,49</t>
+          <t>11,75; 27,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 7,6</t>
+          <t>-8,24; 7,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 11,72</t>
+          <t>-5,05; 11,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 23,59</t>
+          <t>7,6; 24,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,26</t>
+          <t>-4,91; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,89</t>
+          <t>1,76; 12,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 22,8</t>
+          <t>11,07; 23,01</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 234,89</t>
+          <t>-68,35; 303,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,7; 615,41</t>
+          <t>18,75; 779,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,47; 973,94</t>
+          <t>118,6; 1078,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,21; 160,79</t>
+          <t>-66,45; 126,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,05; 223,74</t>
+          <t>-39,74; 232,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33,84; 426,48</t>
+          <t>44,42; 454,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,61; 113,83</t>
+          <t>-51,91; 91,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,68; 259,97</t>
+          <t>17,31; 266,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104,93; 462,51</t>
+          <t>93,77; 461,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,65</t>
+          <t>-4,59; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,89</t>
+          <t>7,72; 15,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,53</t>
+          <t>17,62; 26,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,74</t>
+          <t>-3,47; 2,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,06</t>
+          <t>9,09; 17,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,17; 30,08</t>
+          <t>20,09; 29,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,14</t>
+          <t>-3,03; 1,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,22</t>
+          <t>9,73; 15,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,2; 27,1</t>
+          <t>20,52; 27,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 29,71</t>
+          <t>-52,23; 22,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>85,75; 277,32</t>
+          <t>79,23; 258,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>195,16; 490,86</t>
+          <t>191,82; 456,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 52,99</t>
+          <t>-41,29; 49,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>105,21; 330,28</t>
+          <t>109,37; 330,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>233,43; 562,85</t>
+          <t>235,84; 601,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 18,37</t>
+          <t>-37,67; 17,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>118,61; 253,58</t>
+          <t>115,9; 257,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>242,06; 445,98</t>
+          <t>253,06; 470,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34,57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46,03</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-9,9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>12,49</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,57</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,62</t>
+          <t>27,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33,57</t>
+          <t>36,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,34; -1,72</t>
+          <t>-5,91; 8,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 31,41</t>
+          <t>20,29; 51,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 47,16</t>
+          <t>27,52; 64,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 7,21</t>
+          <t>-19,74; -1,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,72; 51,9</t>
+          <t>-3,98; 29,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,25; 62,08</t>
+          <t>9,23; 48,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 0,72</t>
+          <t>-11,24; 0,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 35,82</t>
+          <t>12,68; 36,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19,09; 48,93</t>
+          <t>22,56; 50,96</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1095,24%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1458,12%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-70,87%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>89,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>182,57%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1095,24%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1350,19%</t>
+          <t>199,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>381,37%</t>
+          <t>415,02%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 353,37</t>
+          <t>183,34; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,1; 520,03</t>
+          <t>305,0; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,74; 8,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>213,62; —</t>
+          <t>-32,25; 331,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>283,3; —</t>
+          <t>36,36; 566,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,59; 49,45</t>
+          <t>-87,84; 54,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,69; 670,47</t>
+          <t>93,04; 596,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>147,85; 875,43</t>
+          <t>181,15; 897,0</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28,61</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>12,32</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23,79</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,61</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,68</t>
+          <t>25,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,39</t>
+          <t>27,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,23</t>
+          <t>-4,28; 3,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,43</t>
+          <t>8,82; 18,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,64; 28,53</t>
+          <t>22,41; 35,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 3,09</t>
+          <t>-4,27; 3,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 19,13</t>
+          <t>7,32; 16,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,46; 32,49</t>
+          <t>19,76; 31,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,05</t>
+          <t>-3,01; 2,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 16,27</t>
+          <t>9,63; 16,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,16; 29,58</t>
+          <t>23,31; 31,69</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-7,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>208,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>439,25%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-6,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>189,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>366,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-7,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>208,85%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>409,57%</t>
+          <t>398,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>390,3%</t>
+          <t>420,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 68,27</t>
+          <t>-48,98; 67,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>83,47; 351,2</t>
+          <t>102,06; 391,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192,45; 631,66</t>
+          <t>260,69; 749,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 64,44</t>
+          <t>-51,06; 72,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>101,6; 407,03</t>
+          <t>81,45; 365,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>229,59; 688,17</t>
+          <t>221,16; 654,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,59; 37,84</t>
+          <t>-39,98; 39,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>120,41; 306,66</t>
+          <t>113,73; 307,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>264,7; 540,76</t>
+          <t>291,47; 616,98</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18,04</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>11,76</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19,54</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,46</t>
+          <t>20,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,48</t>
+          <t>19,23</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 6,74</t>
+          <t>-8,02; 7,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 20,02</t>
+          <t>-5,63; 10,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,75; 27,93</t>
+          <t>8,78; 26,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 7,18</t>
+          <t>-5,83; 5,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 11,16</t>
+          <t>3,65; 20,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,6; 24,07</t>
+          <t>11,52; 28,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 4,53</t>
+          <t>-5,56; 4,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,97</t>
+          <t>1,02; 12,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,07; 23,01</t>
+          <t>13,42; 25,35</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>194,55%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>204,12%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>339,04%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,15%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>166,67%</t>
+          <t>350,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>233,5%</t>
+          <t>256,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-68,35; 303,83</t>
+          <t>-62,09; 149,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,75; 779,36</t>
+          <t>-44,0; 193,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>118,6; 1078,92</t>
+          <t>49,58; 474,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-66,45; 126,38</t>
+          <t>-70,52; 235,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 232,11</t>
+          <t>25,18; 774,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,42; 454,24</t>
+          <t>89,32; 1239,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-51,91; 91,48</t>
+          <t>-53,25; 91,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,31; 266,83</t>
+          <t>3,71; 250,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93,77; 461,5</t>
+          <t>124,17; 552,97</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12,87</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27,04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,63</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22,37</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,87</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,81</t>
+          <t>24,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23,69</t>
+          <t>25,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,27</t>
+          <t>-3,09; 2,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,71</t>
+          <t>8,86; 16,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,62; 26,54</t>
+          <t>22,45; 32,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,53</t>
+          <t>-4,53; 1,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,09; 17,39</t>
+          <t>7,55; 15,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,09; 29,84</t>
+          <t>19,22; 28,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,07</t>
+          <t>-3,07; 1,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,3</t>
+          <t>9,25; 14,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,43</t>
+          <t>22,4; 29,03</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,97%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>192,91%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>405,14%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-21,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>158,58%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>304,99%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-4,97%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>192,91%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>371,71%</t>
+          <t>327,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>338,43%</t>
+          <t>366,09%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 22,77</t>
+          <t>-39,01; 51,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>79,23; 258,15</t>
+          <t>109,15; 321,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191,82; 456,57</t>
+          <t>257,44; 635,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 49,25</t>
+          <t>-50,04; 28,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>109,37; 330,73</t>
+          <t>81,22; 271,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>235,84; 601,88</t>
+          <t>217,28; 526,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 17,56</t>
+          <t>-37,85; 20,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>115,9; 257,19</t>
+          <t>112,14; 258,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>253,06; 470,21</t>
+          <t>272,29; 503,43</t>
         </is>
       </c>
     </row>
